--- a/forms/trg/Formulir_TRG_slfs.xlsx
+++ b/forms/trg/Formulir_TRG_slfs.xlsx
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B27" s="7">
-        <f>COUNTA(Anggota!B5:B23)</f>
+        <f>COUNTA(Anggota!B5:B24)</f>
         <v/>
       </c>
     </row>
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="B28" s="7">
-        <f>COUNTA(Anggota!F5:F23)</f>
+        <f>COUNTA(Anggota!F5:F24)</f>
         <v/>
       </c>
     </row>
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -949,22 +949,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Farah Adila Abdullah</t>
+          <t>Prof. Dr. Syahdar Baba, S.Pt., M.Si.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Faculty of Plantation and Agrotechnology, Universiti Teknologi MARA, Malaysia</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Agricultural Extension</t>
+          <t>Livestock Extension</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -973,13 +969,17 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-7263-8500</t>
-        </is>
-      </c>
-      <c r="K5" s="12" t="n"/>
+          <t>0000-0002-8025-4072</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>6001963</t>
+        </is>
+      </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>55617144200</t>
+          <t>57190666581</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -994,27 +994,39 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Abd. Mutalib</t>
+          <t>Dr. Farah Adila Abdullah</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Master of Science and Technology, Faculty of Animal Science, Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="n"/>
+          <t>Faculty of Plantation and Agrotechnology, Universiti Teknologi MARA, Malaysia</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>Agricultural Extension</t>
+        </is>
+      </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
-      <c r="J6" s="12" t="n"/>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-7263-8500</t>
+        </is>
+      </c>
       <c r="K6" s="12" t="n"/>
-      <c r="L6" s="12" t="n"/>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>55617144200</t>
+        </is>
+      </c>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1027,12 +1039,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Andi Fajar Arfandi</t>
+          <t>Abd. Mutalib</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1060,12 +1072,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Wahyuni</t>
+          <t>Andi Fajar Arfandi</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1093,12 +1105,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Nur Azisah Saleh</t>
+          <t>Wahyuni</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1126,12 +1138,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Wahyudin</t>
+          <t>Nur Azisah Saleh</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1159,12 +1171,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Shifa Zalsabila</t>
+          <t>Wahyudin</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1172,11 +1184,7 @@
           <t>Master of Science and Technology, Faculty of Animal Science, Hasanuddin University</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>Our research activities aim to address structural challenges faced by smallholder farmers, such as limited access to resources, technology, and markets, while improving the efficiency of livestock production to support national food security.</t>
-        </is>
-      </c>
+      <c r="E11" s="11" t="n"/>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
@@ -1194,10 +1202,26 @@
       <c r="A12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="11" t="n"/>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Shifa Zalsabila</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Master of Science and Technology, Faculty of Animal Science, Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Our research activities aim to address structural challenges faced by smallholder farmers, such as limited access to resources, technology, and markets, while improving the efficiency of livestock production to support national food security.</t>
+        </is>
+      </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
@@ -1205,7 +1229,11 @@
       <c r="J12" s="12" t="n"/>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="12" t="n"/>
-      <c r="M12" s="12" t="n"/>
+      <c r="M12" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1394,15 +1422,32 @@
       <c r="L23" s="12" t="n"/>
       <c r="M23" s="12" t="n"/>
     </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="12" t="n"/>
+      <c r="G24" s="12" t="n"/>
+      <c r="H24" s="12" t="n"/>
+      <c r="I24" s="12" t="n"/>
+      <c r="J24" s="12" t="n"/>
+      <c r="K24" s="12" t="n"/>
+      <c r="L24" s="12" t="n"/>
+      <c r="M24" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
